--- a/exports/health_report_20260616.xlsx
+++ b/exports/health_report_20260616.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15 条</t>
+          <t>0 条</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>3 条</t>
+          <t>0 条</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>12 条</t>
+          <t>0 条</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>12 个</t>
+          <t>0 个</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>49.46</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>61.55</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>预警</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>35.19</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>42.6</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -719,531 +719,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>app-server-02</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>[严重] app-server-02 网络带宽容量预警</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>app-server-02</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>[致命] app-server-02 内存容量预警</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>app-server-02</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>cpu</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>[致命] app-server-02 CPU容量预警</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>app-server-01</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[警告] app-server-01 网络带宽容量预警</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>app-server-01</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>[致命] app-server-01 内存容量预警</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>app-server-01</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>cpu</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>[致命] app-server-01 CPU容量预警</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>db-server-01</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>disk</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>[警告] db-server-01 磁盘容量预警</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>db-server-01</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>[致命] db-server-01 内存容量预警</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>db-server-01</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>cpu</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>[警告] db-server-01 CPU容量预警</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>web-server-02</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>[致命] web-server-02 网络带宽容量预警</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>web-server-02</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>[致命] web-server-02 内存容量预警</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>web-server-02</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>cpu</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>[严重] web-server-02 CPU容量预警</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>web-server-01</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>[致命] web-server-01 网络带宽容量预警</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>web-server-01</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>fatal</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>[致命] web-server-01 内存容量预警</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>web-server-01</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>cpu</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>[严重] web-server-01 CPU容量预警</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16 17:31:22</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/health_report_20260616.xlsx
+++ b/exports/health_report_20260616.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>0 条</t>
+          <t>15 条</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>0 条</t>
+          <t>4 条</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>0 条</t>
+          <t>11 条</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0 个</t>
+          <t>11 个</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49.46</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>61.55</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>预警</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>35.19</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42.6</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -719,6 +719,531 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>app-server-02</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>[警告] app-server-02 网络带宽容量预警</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>app-server-02</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>[致命] app-server-02 内存容量预警</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>app-server-02</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>[致命] app-server-02 CPU容量预警</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>app-server-01</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[警告] app-server-01 网络带宽容量预警</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>app-server-01</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>[致命] app-server-01 内存容量预警</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>app-server-01</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>[致命] app-server-01 CPU容量预警</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>db-server-01</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>[警告] db-server-01 磁盘容量预警</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>db-server-01</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>[致命] db-server-01 内存容量预警</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>db-server-01</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>[警告] db-server-01 CPU容量预警</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>web-server-02</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>[致命] web-server-02 网络带宽容量预警</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>web-server-02</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>[致命] web-server-02 内存容量预警</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>web-server-02</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>[致命] web-server-02 CPU容量预警</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>web-server-01</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>[致命] web-server-01 网络带宽容量预警</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>web-server-01</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>[致命] web-server-01 内存容量预警</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>web-server-01</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>[严重] web-server-01 CPU容量预警</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:24:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/health_report_20260616.xlsx
+++ b/exports/health_report_20260616.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>4 条</t>
+          <t>3 条</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>11 条</t>
+          <t>12 条</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>11 个</t>
+          <t>12 个</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[警告] app-server-01 网络带宽容量预警</t>
+          <t>[严重] app-server-01 网络带宽容量预警</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>fatal</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>[严重] web-server-01 CPU容量预警</t>
+          <t>[致命] web-server-01 CPU容量预警</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:24:19</t>
+          <t>2026-06-16 19:00:13</t>
         </is>
       </c>
     </row>
